--- a/public/templates/填空与简答.xlsx
+++ b/public/templates/填空与简答.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,6 +430,9 @@
       <c r="J1" t="str">
         <v>标签</v>
       </c>
+      <c r="K1" t="str">
+        <v>领域</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -462,6 +465,9 @@
       <c r="J2" t="str">
         <v>技术栈</v>
       </c>
+      <c r="K2" t="str">
+        <v>技术栈</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -494,10 +500,13 @@
       <c r="J3" t="str">
         <v>练习</v>
       </c>
+      <c r="K3" t="str">
+        <v>练习</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
   </ignoredErrors>
 </worksheet>
 </file>